--- a/conference_schedule.xlsx
+++ b/conference_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jws780\Documents\GitHub\PS312\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33A44BBD-6BBC-4E6F-92C2-CED64879114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C2380-D34A-4677-AEF4-1E7B0A76D0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B95C5386-F258-451D-B671-22B2B6599F47}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>Group 1</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Alexandra Li</t>
+  </si>
+  <si>
+    <t>Allegra Lief</t>
+  </si>
+  <si>
+    <t>Helena Johannpeter</t>
   </si>
 </sst>
 </file>
@@ -568,7 +574,7 @@
         <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -595,6 +601,9 @@
       <c r="N18" t="s">
         <v>3</v>
       </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -638,6 +647,9 @@
       </c>
       <c r="N26" t="s">
         <v>3</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">

--- a/conference_schedule.xlsx
+++ b/conference_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jws780\Documents\GitHub\PS312\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C2380-D34A-4677-AEF4-1E7B0A76D0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F53051-FEE5-42C6-A5FA-77C6D03E42BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B95C5386-F258-451D-B671-22B2B6599F47}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
   <si>
     <t>Group 1</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Group 4</t>
   </si>
   <si>
-    <t>Cayla Labgold-Carroll, Claire Conner, Hattie Saal,and  Siddarth Sivaraman</t>
-  </si>
-  <si>
     <t>Nonso Onwaeze, Riley Meyer, and Ethan Abisellan</t>
   </si>
   <si>
@@ -114,6 +111,21 @@
   </si>
   <si>
     <t>Helena Johannpeter</t>
+  </si>
+  <si>
+    <t>Group 5</t>
+  </si>
+  <si>
+    <t>Asha Mehta, Luiza Lima, Sabrina Zhang, and Christian Windham</t>
+  </si>
+  <si>
+    <t>Cayla Labgold-Carroll, Claire Conner, Hattie Saal, and Siddarth Sivaraman</t>
+  </si>
+  <si>
+    <t>Bethel Asfaw</t>
+  </si>
+  <si>
+    <t>Cayla Labgold-Carroll</t>
   </si>
 </sst>
 </file>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B7DB03-3475-4F60-B7DD-2CEA436CC48A}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -513,7 +525,7 @@
         <v>3</v>
       </c>
       <c r="P3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -527,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="P5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -541,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="P7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -554,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N12" t="s">
         <v>3</v>
       </c>
       <c r="P12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -568,13 +580,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14" t="s">
         <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -582,13 +594,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N16" t="s">
         <v>3</v>
       </c>
       <c r="P16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -596,70 +608,95 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N18" t="s">
         <v>3</v>
       </c>
       <c r="P18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>46170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" t="s">
         <v>3</v>
       </c>
       <c r="P24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N26" t="s">
         <v>3</v>
       </c>
       <c r="P26" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="N28" t="s">
+        <v>3</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>11</v>
       </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28" t="s">
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
         <v>3</v>
       </c>
     </row>

--- a/conference_schedule.xlsx
+++ b/conference_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jws780\Documents\GitHub\PS312\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F53051-FEE5-42C6-A5FA-77C6D03E42BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFFC745-912A-4C9E-9C3A-E33C1001BBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B95C5386-F258-451D-B671-22B2B6599F47}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Group 1</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Cayla Labgold-Carroll</t>
+  </si>
+  <si>
+    <t>Kamau Edmondson, Alisande Jaiserrisingh, Chloe Park, Helen Pacheco, Ivani Phillips</t>
   </si>
 </sst>
 </file>
@@ -506,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B7DB03-3475-4F60-B7DD-2CEA436CC48A}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -556,147 +559,158 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>46168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="N12" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="N14" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N16" t="s">
         <v>3</v>
       </c>
       <c r="P16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N18" t="s">
         <v>3</v>
       </c>
       <c r="P18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N20" t="s">
         <v>3</v>
       </c>
       <c r="P20" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>46170</v>
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="N22" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="N24" t="s">
         <v>3</v>
       </c>
       <c r="P24" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="N26" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" t="s">
-        <v>22</v>
+      <c r="A26" s="1">
+        <v>46170</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N28" t="s">
         <v>3</v>
       </c>
       <c r="P28" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="N30" t="s">
         <v>3</v>
+      </c>
+      <c r="P30" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>25</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>26</v>
       </c>
-      <c r="N32" t="s">
+      <c r="N36" t="s">
         <v>3</v>
       </c>
     </row>

--- a/conference_schedule.xlsx
+++ b/conference_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jws780\Documents\GitHub\PS312\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFFC745-912A-4C9E-9C3A-E33C1001BBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69508066-317A-47C4-A14D-1959BDFEDD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B95C5386-F258-451D-B671-22B2B6599F47}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>Group 1</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>Kamau Edmondson, Alisande Jaiserrisingh, Chloe Park, Helen Pacheco, Ivani Phillips</t>
+  </si>
+  <si>
+    <t>Nikhil Quintin</t>
+  </si>
+  <si>
+    <t>Liana Liu Ioannides</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -702,8 +708,11 @@
       <c r="N34" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -712,6 +721,9 @@
       </c>
       <c r="N36" t="s">
         <v>3</v>
+      </c>
+      <c r="P36" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
